--- a/Asignaciones/Tablero/temp_html1.xlsx
+++ b/Asignaciones/Tablero/temp_html1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="plantilla" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Participantes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="plantilla" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Participantes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_Hlk52262180" localSheetId="0">plantilla!#REF!</definedName>
@@ -797,18 +797,21 @@
       </c>
       <c r="I2" s="42" t="inlineStr">
         <is>
-          <t>9-15 DE MARZO</t>
+          <t>5-11 DE OCTUBRE</t>
         </is>
       </c>
       <c r="J2" s="42" t="inlineStr">
         <is>
-          <t>ISAÍAS 43, 44</t>
+          <t>JEREMÍAS 40, 41</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Edwin Encalada</t>
-        </is>
+          <t>Vinicio Cóndor</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="3" ht="12.6" customHeight="1" s="27">
@@ -828,7 +831,7 @@
       <c r="J3" s="42" t="n"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Manuel Vizcaino</t>
+          <t>Santiago Inagan</t>
         </is>
       </c>
     </row>
@@ -856,13 +859,13 @@
       </c>
       <c r="I4" s="42" t="inlineStr">
         <is>
-          <t>Canción 63: ¡Soy testigo de Jehová!</t>
+          <t>Canción 33: Echa sobre Dios tu carga</t>
         </is>
       </c>
       <c r="J4" s="42" t="n"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Abel Peralta</t>
+          <t>Santiago Tipantuña</t>
         </is>
       </c>
     </row>
@@ -922,7 +925,7 @@
       </c>
       <c r="I7" s="42" t="inlineStr">
         <is>
-          <t>1. Una profecía escrita dos siglos antes de su cumplimiento</t>
+          <t>1. Tengamos un punto de vista equilibrado de la protección de Jehová</t>
         </is>
       </c>
       <c r="J7" s="42" t="inlineStr">
@@ -932,7 +935,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Israel Rocha</t>
+          <t>Dilan Murillo</t>
         </is>
       </c>
     </row>
@@ -957,7 +960,7 @@
       <c r="J8" s="42" t="n"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Jaime Mera</t>
+          <t>Byron Vela</t>
         </is>
       </c>
     </row>
@@ -991,22 +994,12 @@
       <c r="J9" s="42" t="n"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Kenneth López</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>3. Lectura de la Biblia</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>4 mins.</t>
+          <t>Alex Calvache</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Jorge Bolaños</t>
+          <t>Wilson Rodriguez</t>
         </is>
       </c>
       <c r="R9" s="2" t="n"/>
@@ -1062,7 +1055,7 @@
       <c r="J11" s="42" t="n"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Pedro Apolinario</t>
+          <t>Rosa Ramirez</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1072,12 +1065,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1 min.</t>
+          <t>2 mins.</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Fernando Cajas</t>
+          <t>Lucila de Moreano</t>
         </is>
       </c>
       <c r="R11" s="2" t="n"/>
@@ -1086,12 +1079,12 @@
     <row r="12" ht="13.8" customHeight="1" s="27">
       <c r="K12" t="inlineStr">
         <is>
-          <t>Jhon Jairo Cabrera</t>
+          <t>Jessica Guilcazo</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Ezequiel Ortega</t>
+          <t>Nataly Quiñonez</t>
         </is>
       </c>
       <c r="R12" s="2" t="n"/>
@@ -1127,7 +1120,7 @@
       <c r="J13" s="42" t="n"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Daysi Espinoza</t>
+          <t>Myrian de Jato</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1137,12 +1130,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3 mins.</t>
+          <t>2 mins.</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Cristina de Fernandez</t>
+          <t>Abigail Rodriguez</t>
         </is>
       </c>
       <c r="R13" s="2" t="n"/>
@@ -1151,12 +1144,12 @@
     <row r="14" ht="13.8" customHeight="1" s="27">
       <c r="K14" t="inlineStr">
         <is>
-          <t>Blanca de Condor</t>
+          <t>Maricela Reyna</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Geovanna Cedeño</t>
+          <t>Francia de Brito</t>
         </is>
       </c>
       <c r="R14" s="2" t="n"/>
@@ -1192,7 +1185,7 @@
       <c r="J15" s="42" t="n"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Maricela de Montes</t>
+          <t>Eva de Aguilera</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1202,12 +1195,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>3 mins.</t>
+          <t>4 mins.</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Jenyffer Cadena</t>
+          <t>Martha de Quilachamin</t>
         </is>
       </c>
       <c r="R15" s="2" t="n"/>
@@ -1216,12 +1209,12 @@
     <row r="16" ht="13.8" customHeight="1" s="27">
       <c r="K16" t="inlineStr">
         <is>
-          <t>Abigail Rodriguez</t>
+          <t>Silvia Armijos</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Myrian de Jato</t>
+          <t>Olga de Campaña</t>
         </is>
       </c>
       <c r="R16" s="2" t="n"/>
@@ -1258,22 +1251,22 @@
       <c r="J17" s="42" t="n"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Nataly Quiñonez</t>
+          <t>Pablo Morales</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7. Haga revisitas</t>
+          <t>7. Explique sus creencias</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>4 mins.</t>
+          <t>3 mins.</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Marlene de Rocha</t>
+          <t>Freddy Velazco</t>
         </is>
       </c>
       <c r="R17" s="2" t="n"/>
@@ -1282,12 +1275,12 @@
     <row r="18" ht="13.8" customHeight="1" s="27">
       <c r="K18" t="inlineStr">
         <is>
-          <t>Marlene Molina</t>
+          <t>José Carrera</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Paola de Lagla</t>
+          <t>Francisco Vizuete</t>
         </is>
       </c>
       <c r="R18" s="2" t="n"/>
@@ -1315,7 +1308,7 @@
       <c r="H20" s="39" t="n"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Canción 69: Prediquen las nuevas del Reino</t>
+          <t>Canción 17: “Quiero”</t>
         </is>
       </c>
       <c r="J20" s="23" t="n"/>
@@ -1337,8 +1330,21 @@
         <f>+K21</f>
         <v/>
       </c>
-      <c r="I21" s="42" t="n"/>
-      <c r="J21" s="42" t="n"/>
+      <c r="I21" s="42" t="inlineStr">
+        <is>
+          <t>8. Jehová protege a las viudas — Análisis con el auditorio.</t>
+        </is>
+      </c>
+      <c r="J21" s="42" t="inlineStr">
+        <is>
+          <t>15 mins.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>David Quiñonez</t>
+        </is>
+      </c>
       <c r="Q21" s="14" t="n"/>
       <c r="R21" s="20" t="n"/>
     </row>
@@ -1367,6 +1373,11 @@
       </c>
       <c r="I22" s="42" t="n"/>
       <c r="J22" s="42" t="n"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Jandri Orozco</t>
+        </is>
+      </c>
       <c r="Q22" s="20" t="n"/>
       <c r="R22" s="20" t="n"/>
     </row>
@@ -1377,6 +1388,11 @@
       </c>
       <c r="I23" s="42" t="n"/>
       <c r="J23" s="42" t="n"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Darwin Guillén</t>
+        </is>
+      </c>
       <c r="Q23" s="19" t="n"/>
     </row>
     <row r="24" ht="12.6" customHeight="1" s="27">
@@ -1424,13 +1440,13 @@
       </c>
       <c r="I25" s="42" t="inlineStr">
         <is>
-          <t>Canción 137: Fieles, valiosas, amadas</t>
+          <t>Canción 38: Jehová te cuidará</t>
         </is>
       </c>
       <c r="J25" s="42" t="n"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Carlos Pastás</t>
+          <t>Marcelo Moreano</t>
         </is>
       </c>
       <c r="Q25" s="14" t="n"/>
